--- a/business_forms/037_team_meeting_discussion_topics_form--business_forms.xlsx
+++ b/business_forms/037_team_meeting_discussion_topics_form--business_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="29" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="48" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -520,15 +520,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>topic_1</t>
+          <t>main_topic</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Meeting Topic 1</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Meeting Topic</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Please describe the main topic of the meeting.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>yes</t>
@@ -543,15 +547,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>topic_2</t>
+          <t>discussion_questions</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Meeting Topic 2</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Meeting Questions</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>What are the key questions to be discussed?</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>yes</t>
@@ -566,17 +574,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>meeting_question_1</t>
+          <t>meeting_agenda</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Meeting Question 1</t>
+          <t>Meeting Agenda</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>What would you like to ask?</t>
+          <t>What is the meeting agenda?</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -588,20 +596,24 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>meeting_question_2</t>
+          <t>meeting_date</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Meeting Question 2</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>Meeting Date</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>What is the meeting date?</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>yes</t>
@@ -611,20 +623,24 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>question_5</t>
+          <t>meeting_time</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Question 1</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Meeting Time</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>What is the meeting time?</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>yes</t>
@@ -639,15 +655,19 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>meeting_agenda_1</t>
+          <t>meeting_location</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Meeting Agenda 1</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Meeting Location</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Where will the meeting take place?</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>yes</t>
@@ -662,15 +682,19 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>meeting_agenda_2</t>
+          <t>attendees</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Meeting Agenda 2</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>Attendees</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Who will attend the meeting?</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>yes</t>
@@ -685,7 +709,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>meeting_note_1</t>
+          <t>meeting_note</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -693,7 +717,11 @@
           <t>Meeting Notes</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Are there any meeting notes or minutes?</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>yes</t>
@@ -703,20 +731,24 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>meeting_date_1</t>
+          <t>follow_up_action_item</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Meeting Date</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Follow-up Action Item</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Is there a follow-up action item?</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>yes</t>
@@ -726,46 +758,54 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>meeting_time_1</t>
+          <t>next_meeting_date</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Meeting Time</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>Next Meeting Date</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>What is the next meeting date?</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>meeting_location_1</t>
+          <t>next_meeting_time</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Meeting Location</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>Next Meeting Time</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>What is the next meeting time?</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -777,18 +817,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>question_12</t>
+          <t>meeting_location_change</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Meeting Location</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>Meeting Location Change</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Is there a meeting location change?</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -800,15 +844,19 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>question_13</t>
+          <t>meeting_topic</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Meeting Location</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>Meeting Topic (2)</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>What is the meeting topic?</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>yes</t>
@@ -818,20 +866,24 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>attendees_1</t>
+          <t>meeting_question</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Attendees</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>Meeting Question</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>What is the meeting question?</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>yes</t>
@@ -851,13 +903,17 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Question 15</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>Meeting Question 1</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>This is the first question</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -869,18 +925,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>attendees_2</t>
+          <t>question_16</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Attendees</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>Meeting Question 2</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>This is the second question</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -892,15 +952,19 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>attendees_3</t>
+          <t>meeting_agenda_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Attendees</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
+          <t>Meeting Agenda 2</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>What is the meeting agenda?</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>yes</t>
@@ -915,183 +979,22 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>meeting_location_2</t>
+          <t>meeting_topic_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Meeting Location</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
+          <t>Meeting Topic 2 (1)</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>What is the meeting topic?</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>meeting_topic_1</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Meeting Topic</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>question_20</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Meeting Topic</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>meeting_question_2</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Meeting Question</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>What is the question?</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>meeting_note_2</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Meeting Note</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>meeting_agenda_3</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Meeting Agenda</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
           <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>question_24</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Meeting Agenda</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>question_25</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Meeting Agenda</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1106,11 +1009,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
@@ -1134,68 +1037,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>question_5_choices</t>
+          <t>meeting_question_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>question_5_choices</t>
+          <t>meeting_question_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>meeting_question_2_choices</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>meeting_question_2_choices</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
